--- a/data/Summary Forecast Production.xlsx
+++ b/data/Summary Forecast Production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sandag-my.sharepoint.com/personal/cra_sandag_org/Documents/Documents/GitHub/Population-Sim/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sandag-my.sharepoint.com/personal/gsc_sandag_org/Documents/VSCode Projects/Python/Population-Sim/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{096A7BE1-4EFA-494A-8685-017AD9B29A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{096A7BE1-4EFA-494A-8685-017AD9B29A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D241E9-E133-4386-A948-C7670FF549FB}"/>
   <bookViews>
-    <workbookView xWindow="-16200" yWindow="3510" windowWidth="20805" windowHeight="17625" xr2:uid="{92465A71-E44C-4FA6-BF4B-DC8AE12CC5FD}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14976" windowHeight="19368" xr2:uid="{92465A71-E44C-4FA6-BF4B-DC8AE12CC5FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -487,12 +487,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DD6DB0-C64D-4E12-AF64-3608E8545E84}">
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="11" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +522,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -550,7 +551,7 @@
         <v>9.4412851609636377</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -579,7 +580,7 @@
         <v>1.2228539820782416</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -608,7 +609,7 @@
         <v>3.050425233527033</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -637,7 +638,7 @@
         <v>69.884190964489576</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -666,7 +667,7 @@
         <v>171.40868139227817</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -695,7 +696,7 @@
         <v>31.373702732286176</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -724,7 +725,7 @@
         <v>92.247670508370589</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -753,7 +754,7 @@
         <v>58.38592408295839</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -782,7 +783,7 @@
         <v>17.293399775419424</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -811,7 +812,7 @@
         <v>54.902711849372089</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -840,7 +841,7 @@
         <v>62.263835233560805</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -869,7 +870,7 @@
         <v>207.33636430961744</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -898,7 +899,7 @@
         <v>21.460344131120404</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -927,7 +928,7 @@
         <v>97.028363375937246</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -956,7 +957,7 @@
         <v>140.36649041960186</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -985,7 +986,7 @@
         <v>187.57706110573596</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1014,7 +1015,7 @@
         <v>49.210795460225761</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1043,7 +1044,7 @@
         <v>14.292743180927809</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1072,7 +1073,7 @@
         <v>130.38627549733593</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1101,7 +1102,7 @@
         <v>69.708553329604001</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1130,7 +1131,7 @@
         <v>57.019836718498517</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1159,7 +1160,7 @@
         <v>48.036408640711095</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1188,7 +1189,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1217,7 +1218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
